--- a/ML data/Store Max Items.xlsx
+++ b/ML data/Store Max Items.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\Desktop\inventoryprediction\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\Desktop\inventoryprediction\ML data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95190AEC-0FA7-4F6A-906A-8BFEF928E2C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25FBB17-3468-40F4-9E34-843F4ACA8C77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23565" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{F7753A57-749A-43F5-B214-517651157AC9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{F7753A57-749A-43F5-B214-517651157AC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="107">
   <si>
     <t>Store</t>
   </si>
@@ -65,9 +65,6 @@
     <t>Lavender</t>
   </si>
   <si>
-    <t>Agave</t>
-  </si>
-  <si>
     <t>Condensed Milk</t>
   </si>
   <si>
@@ -143,24 +140,9 @@
     <t>Espresso Trash Bag</t>
   </si>
   <si>
-    <t>Matcha Bag</t>
-  </si>
-  <si>
     <t>Vanilla Syrup</t>
   </si>
   <si>
-    <t>Cold Brew Concentrate</t>
-  </si>
-  <si>
-    <t>Vienna</t>
-  </si>
-  <si>
-    <t>BC</t>
-  </si>
-  <si>
-    <t>Strawberry Puree</t>
-  </si>
-  <si>
     <t>Matcha Drizzle</t>
   </si>
   <si>
@@ -206,12 +188,6 @@
     <t>Beverage Napkin</t>
   </si>
   <si>
-    <t>Cup Carriers</t>
-  </si>
-  <si>
-    <t>Straws</t>
-  </si>
-  <si>
     <t>Wooden Stir Stick</t>
   </si>
   <si>
@@ -287,9 +263,6 @@
     <t>Paper BIG Bag</t>
   </si>
   <si>
-    <t>Strawberry</t>
-  </si>
-  <si>
     <t>Almond</t>
   </si>
   <si>
@@ -360,6 +333,30 @@
   </si>
   <si>
     <t>White trash bag</t>
+  </si>
+  <si>
+    <t>Vienna Cream</t>
+  </si>
+  <si>
+    <t>Buttercream</t>
+  </si>
+  <si>
+    <t>M1200 Matcha</t>
+  </si>
+  <si>
+    <t>Strawberry Puree Cases</t>
+  </si>
+  <si>
+    <t>4 Cup Carrier</t>
+  </si>
+  <si>
+    <t>Agave Cases</t>
+  </si>
+  <si>
+    <t>Black Straws</t>
+  </si>
+  <si>
+    <t>Coldbrew Concentrate</t>
   </si>
 </sst>
 </file>
@@ -752,7 +749,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -763,7 +760,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -774,7 +771,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -785,7 +782,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -796,7 +793,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -807,7 +804,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -818,43 +815,43 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -862,10 +859,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -873,10 +870,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -884,10 +881,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -895,10 +892,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -906,10 +903,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -917,10 +914,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -928,10 +925,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -939,10 +936,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -950,10 +947,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -961,10 +958,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -972,10 +969,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -983,10 +980,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -994,10 +991,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1005,10 +1002,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1016,10 +1013,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1027,10 +1024,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27">
         <v>2</v>
@@ -1038,10 +1035,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28">
         <v>2</v>
@@ -1049,10 +1046,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29">
         <v>2</v>
@@ -1060,10 +1057,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -1071,10 +1068,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1082,10 +1079,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1093,10 +1090,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1104,10 +1101,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="C34">
         <v>4</v>
@@ -1115,10 +1112,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -1126,10 +1123,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
+        <v>106</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -1137,10 +1134,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="C37">
         <v>20</v>
@@ -1148,10 +1145,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="C38">
         <v>8</v>
@@ -1159,10 +1156,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>102</v>
       </c>
       <c r="C39">
         <v>4</v>
@@ -1170,10 +1167,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C40">
         <v>2</v>
@@ -1181,10 +1178,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1192,10 +1189,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C42">
         <v>1</v>
@@ -1203,10 +1200,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B43" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1214,10 +1211,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -1225,10 +1222,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1236,10 +1233,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1247,10 +1244,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1258,10 +1255,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1269,10 +1266,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C49">
         <v>5</v>
@@ -1280,10 +1277,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C50">
         <v>10</v>
@@ -1291,10 +1288,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -1302,10 +1299,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1313,10 +1310,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -1324,10 +1321,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1335,10 +1332,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1346,10 +1343,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -1357,10 +1354,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C57">
         <v>21</v>
@@ -1368,10 +1365,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C58">
         <v>3</v>
@@ -1379,10 +1376,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C59">
         <v>5</v>
@@ -1390,10 +1387,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C60">
         <v>4</v>
@@ -1401,10 +1398,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B61" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C61">
         <v>1</v>
@@ -1412,10 +1409,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -1423,10 +1420,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B63" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -1434,10 +1431,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -1445,10 +1442,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C65">
         <v>10</v>
@@ -1456,10 +1453,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -1467,10 +1464,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -1478,10 +1475,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -1489,10 +1486,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -1500,10 +1497,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -1511,10 +1508,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -1522,10 +1519,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -1533,10 +1530,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B73" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -1544,10 +1541,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B74" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -1555,10 +1552,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B75" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C75">
         <v>2</v>
@@ -1566,10 +1563,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B76" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C76">
         <v>3</v>
@@ -1577,10 +1574,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -1588,10 +1585,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -1599,10 +1596,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C79">
         <v>3</v>
@@ -1610,10 +1607,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B80" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C80">
         <v>2</v>
@@ -1621,10 +1618,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B81" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -1632,10 +1629,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B82" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -1643,10 +1640,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B83" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -1654,10 +1651,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="C84">
         <v>4</v>
@@ -1665,10 +1662,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="C85">
         <v>2</v>
@@ -1676,7 +1673,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B86" t="s">
         <v>6</v>
@@ -1687,10 +1684,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B87" t="s">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="C87">
         <v>3</v>
@@ -1698,10 +1695,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>65</v>
+      </c>
+      <c r="B88" t="s">
         <v>73</v>
-      </c>
-      <c r="B88" t="s">
-        <v>81</v>
       </c>
       <c r="C88">
         <v>2</v>
@@ -1709,10 +1706,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B89" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -1720,10 +1717,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B90" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C90">
         <v>2</v>
@@ -1731,10 +1728,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B91" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C91">
         <v>3</v>
@@ -1742,10 +1739,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B92" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C92">
         <v>3</v>
@@ -1753,10 +1750,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B93" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C93">
         <v>8</v>
@@ -1764,10 +1761,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B94" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -1775,10 +1772,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -1786,10 +1783,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B96" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -1797,10 +1794,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B97" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -1808,10 +1805,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B98" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C98">
         <v>2</v>
@@ -1819,10 +1816,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B99" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C99">
         <v>2</v>
@@ -1830,10 +1827,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B100" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C100">
         <v>2</v>
@@ -1841,10 +1838,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B101" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C101">
         <v>2</v>
@@ -1852,10 +1849,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B102" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -1863,10 +1860,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B103" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -1874,10 +1871,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B104" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -1885,10 +1882,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B105" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -1896,10 +1893,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B106" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -1907,10 +1904,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B107" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C107">
         <v>2</v>
@@ -1918,10 +1915,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B108" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C108">
         <v>2</v>
@@ -1929,10 +1926,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B109" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -1940,10 +1937,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B110" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C110">
         <v>2</v>
@@ -1951,10 +1948,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B111" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C111">
         <v>2</v>
@@ -1962,10 +1959,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B112" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -1973,10 +1970,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B113" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C113">
         <v>1</v>
@@ -1984,10 +1981,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B114" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -1995,10 +1992,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B115" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C115">
         <v>1</v>
@@ -2006,10 +2003,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B116" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="C116">
         <v>5</v>
@@ -2017,10 +2014,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B117" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C117">
         <v>2</v>
@@ -2028,10 +2025,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C118">
         <v>2</v>
@@ -2039,10 +2036,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B119" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C119">
         <v>1</v>
@@ -2050,10 +2047,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B120" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -2061,10 +2058,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B121" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C121">
         <v>3</v>
@@ -2072,10 +2069,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B122" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C122">
         <v>30</v>
@@ -2083,10 +2080,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B123" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -2094,10 +2091,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B124" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -2105,10 +2102,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B125" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -2116,10 +2113,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B126" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C126">
         <v>7</v>
@@ -2127,10 +2124,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B127" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -2138,10 +2135,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B128" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C128">
         <v>6</v>
@@ -2149,10 +2146,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B129" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C129">
         <v>8</v>
@@ -2160,10 +2157,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B130" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -2171,10 +2168,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B131" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C131">
         <v>1</v>
